--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 12.01.2026 a 18.01.2026.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 12.01.2026 a 18.01.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{216DEFE2-F625-411C-85F1-467E2FC84B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{362DBC96-E4D9-4616-BF30-1479A34B965E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="12.01" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="60">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -150,6 +150,78 @@
   </si>
   <si>
     <t xml:space="preserve">FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: CHASSI. LUZ DA INJEÇÃO ELETRONICA ACESA. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAIO SANTOS MONTENEGRO REGO                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILMO CRISPIN DE OLIVEIRA                    </t>
+  </si>
+  <si>
+    <t>Desistência;</t>
+  </si>
+  <si>
+    <t>Pedido do segurado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAIRA RAMOS SANTANA MOREIRA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIO BAGGIO                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEF DE SOUZA DO NASCIMENTO                  </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE N CORRIGIU AS FOTOS INCORRETAS. FOTOS INCORRETAS: Painel com a motocicleta ligada. KM TOTAL INDISPONIVEL. CARENAGEM ESQ E DIR ARRANHADA 2P. PARALAMA D. ARRANHADA 1P. MOTOR ARRANHADO 1P.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDERSON PATRICK JATI FERNANDES              </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: CRLV. KM TOTAL INDISPONIVEL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIA ROSI MARY CAVALCANTE DE GOIS         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARILDA SOARES COIMBRA                       </t>
+  </si>
+  <si>
+    <t>Duplicidade;</t>
+  </si>
+  <si>
+    <t>Veículo em duplicidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO CARDIA DA FONSECA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLEANA ARAUJO DA SILVA ALVES                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAYNARA DE MORAIS BASTOS REZENDE            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAPHAEL FERREIRA DA CRUZ                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AELCIO FERREIRA DOS SANTOS                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO BOTASSINI                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDEMIR VIEIRA DE MELO                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO FONTES ROCHA SILVA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO VITOR DOS SANTOS                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THIAGO SILVA QUEIROZ SANTANA                 </t>
   </si>
 </sst>
 </file>
@@ -208,7 +280,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -440,12 +512,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -576,9 +659,6 @@
     <xf numFmtId="14" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -590,9 +670,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -624,7 +701,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -634,26 +710,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1035,19 +1111,19 @@
       <c r="C2" s="25">
         <v>46034</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="74">
+      <c r="E2" s="22">
         <v>3450211677</v>
       </c>
-      <c r="F2" s="65" t="s">
+      <c r="F2" s="63" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="65" t="s">
+      <c r="H2" s="63" t="s">
         <v>13</v>
       </c>
       <c r="I2" s="44"/>
@@ -1062,16 +1138,16 @@
       <c r="C3" s="25">
         <v>46034</v>
       </c>
-      <c r="D3" s="74">
+      <c r="D3" s="22">
         <v>136096806</v>
       </c>
       <c r="E3" s="17">
         <v>3450204076</v>
       </c>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="71" t="s">
+      <c r="G3" s="68" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="45" t="s">
@@ -1091,16 +1167,16 @@
       <c r="C4" s="25">
         <v>46034</v>
       </c>
-      <c r="D4" s="74">
+      <c r="D4" s="22">
         <v>136097889</v>
       </c>
       <c r="E4" s="17">
         <v>3450205154</v>
       </c>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="71" t="s">
+      <c r="G4" s="68" t="s">
         <v>18</v>
       </c>
       <c r="H4" s="45" t="s">
@@ -1120,16 +1196,16 @@
       <c r="C5" s="25">
         <v>46034</v>
       </c>
-      <c r="D5" s="74">
+      <c r="D5" s="22">
         <v>136097912</v>
       </c>
       <c r="E5" s="17">
         <v>3450205176</v>
       </c>
-      <c r="F5" s="70" t="s">
+      <c r="F5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="68" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="45" t="s">
@@ -1149,16 +1225,16 @@
       <c r="C6" s="25">
         <v>46034</v>
       </c>
-      <c r="D6" s="74">
+      <c r="D6" s="22">
         <v>136118420</v>
       </c>
       <c r="E6" s="17">
         <v>3450206804</v>
       </c>
-      <c r="F6" s="70" t="s">
+      <c r="F6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="71" t="s">
+      <c r="G6" s="68" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="45" t="s">
@@ -1178,16 +1254,16 @@
       <c r="C7" s="25">
         <v>46034</v>
       </c>
-      <c r="D7" s="74">
+      <c r="D7" s="22">
         <v>136141649</v>
       </c>
       <c r="E7" s="17">
         <v>3450209378</v>
       </c>
-      <c r="F7" s="70" t="s">
+      <c r="F7" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="71" t="s">
+      <c r="G7" s="68" t="s">
         <v>25</v>
       </c>
       <c r="H7" s="46" t="s">
@@ -1207,16 +1283,16 @@
       <c r="C8" s="25">
         <v>46034</v>
       </c>
-      <c r="D8" s="74">
+      <c r="D8" s="22">
         <v>136182419</v>
       </c>
       <c r="E8" s="17">
         <v>3450212766</v>
       </c>
-      <c r="F8" s="70" t="s">
+      <c r="F8" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="71" t="s">
+      <c r="G8" s="68" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="46" t="s">
@@ -1236,16 +1312,16 @@
       <c r="C9" s="25">
         <v>46034</v>
       </c>
-      <c r="D9" s="74">
+      <c r="D9" s="22">
         <v>136124406</v>
       </c>
       <c r="E9" s="17">
         <v>3450207520</v>
       </c>
-      <c r="F9" s="70" t="s">
+      <c r="F9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="71" t="s">
+      <c r="G9" s="68" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="45" t="s">
@@ -1265,16 +1341,16 @@
       <c r="C10" s="25">
         <v>46034</v>
       </c>
-      <c r="D10" s="74">
+      <c r="D10" s="22">
         <v>136127880</v>
       </c>
       <c r="E10" s="17">
         <v>3450208080</v>
       </c>
-      <c r="F10" s="70" t="s">
+      <c r="F10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="71" t="s">
+      <c r="G10" s="68" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="45" t="s">
@@ -1294,16 +1370,16 @@
       <c r="C11" s="25">
         <v>46034</v>
       </c>
-      <c r="D11" s="74">
+      <c r="D11" s="22">
         <v>136125004</v>
       </c>
       <c r="E11" s="17">
         <v>3450207618</v>
       </c>
-      <c r="F11" s="70" t="s">
+      <c r="F11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="71" t="s">
+      <c r="G11" s="68" t="s">
         <v>18</v>
       </c>
       <c r="H11" s="45" t="s">
@@ -1323,16 +1399,16 @@
       <c r="C12" s="25">
         <v>46034</v>
       </c>
-      <c r="D12" s="74">
+      <c r="D12" s="22">
         <v>136098289</v>
       </c>
       <c r="E12" s="17">
         <v>3450205264</v>
       </c>
-      <c r="F12" s="70" t="s">
+      <c r="F12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="71" t="s">
+      <c r="G12" s="68" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="45" t="s">
@@ -1346,8 +1422,8 @@
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="25"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="56"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="55"/>
       <c r="F13" s="31"/>
       <c r="G13" s="42"/>
       <c r="H13" s="45"/>
@@ -1494,17 +1570,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
     <col min="3" max="3" width="21.5703125" customWidth="1"/>
     <col min="4" max="4" width="27.7109375" style="16" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="5" max="6" width="31.5703125" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" customWidth="1"/>
+    <col min="8" max="8" width="29.5703125" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1518,19 +1593,19 @@
       <c r="C1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="74" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="52" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="50" t="s">
@@ -1541,255 +1616,539 @@
       <c r="A2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="58"/>
+      <c r="B2" s="53">
+        <v>46022</v>
+      </c>
+      <c r="C2" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D2" s="75">
+        <v>136076382</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450202877</v>
+      </c>
+      <c r="F2" s="71" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="56">
+        <v>46022</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="44"/>
+      <c r="B3" s="7">
+        <v>46054</v>
+      </c>
+      <c r="C3" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D3" s="75">
+        <v>136088990</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3450204439</v>
+      </c>
+      <c r="F3" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="68" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="44">
+        <v>46034</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="44"/>
+      <c r="B4" s="7">
+        <v>46022</v>
+      </c>
+      <c r="C4" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D4" s="75">
+        <v>136078456</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450189061</v>
+      </c>
+      <c r="F4" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="44">
+        <v>46022</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="44"/>
+      <c r="B5" s="7">
+        <v>46027</v>
+      </c>
+      <c r="C5" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D5" s="75">
+        <v>136098801</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450205352</v>
+      </c>
+      <c r="F5" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="44">
+        <v>46027</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="44"/>
+      <c r="B6" s="7">
+        <v>46027</v>
+      </c>
+      <c r="C6" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D6" s="75">
+        <v>136104011</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450205803</v>
+      </c>
+      <c r="F6" s="71" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="44">
+        <v>46027</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="44"/>
+      <c r="B7" s="7">
+        <v>46014</v>
+      </c>
+      <c r="C7" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D7" s="75">
+        <v>136110987</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450195947</v>
+      </c>
+      <c r="F7" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="44">
+        <v>46014</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="44"/>
+      <c r="B8" s="7">
+        <v>46030</v>
+      </c>
+      <c r="C8" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D8" s="75">
+        <v>136170856</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450211226</v>
+      </c>
+      <c r="F8" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="44">
+        <v>46030</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="44"/>
+      <c r="B9" s="7">
+        <v>46029</v>
+      </c>
+      <c r="C9" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D9" s="75">
+        <v>136140036</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450209246</v>
+      </c>
+      <c r="F9" s="71" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="44">
+        <v>46035</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="44"/>
+      <c r="B10" s="7">
+        <v>46031</v>
+      </c>
+      <c r="C10" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D10" s="75">
+        <v>136184781</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450212975</v>
+      </c>
+      <c r="F10" s="71" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="44">
+        <v>46031</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="44"/>
+      <c r="B11" s="7">
+        <v>46031</v>
+      </c>
+      <c r="C11" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D11" s="75">
+        <v>136170601</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450211523</v>
+      </c>
+      <c r="F11" s="71" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="44">
+        <v>46031</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="44"/>
+      <c r="B12" s="7">
+        <v>46022</v>
+      </c>
+      <c r="C12" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D12" s="75">
+        <v>136074390</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450202712</v>
+      </c>
+      <c r="F12" s="71" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="44">
+        <v>46022</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="44"/>
+      <c r="B13" s="7">
+        <v>46022</v>
+      </c>
+      <c r="C13" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D13" s="75">
+        <v>136075052</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450202756</v>
+      </c>
+      <c r="F13" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="44">
+        <v>46022</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="44"/>
+      <c r="B14" s="7">
+        <v>46022</v>
+      </c>
+      <c r="C14" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D14" s="75">
+        <v>136075688</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450202811</v>
+      </c>
+      <c r="F14" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="44">
+        <v>46022</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="44"/>
+      <c r="B15" s="7">
+        <v>46021</v>
+      </c>
+      <c r="C15" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D15" s="75">
+        <v>136078295</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450202657</v>
+      </c>
+      <c r="F15" s="71" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="44">
+        <v>46021</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="44"/>
+      <c r="B16" s="7">
+        <v>46024</v>
+      </c>
+      <c r="C16" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D16" s="75">
+        <v>136081242</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450203251</v>
+      </c>
+      <c r="F16" s="71" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="44">
+        <v>46024</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="44"/>
+      <c r="B17" s="7">
+        <v>46024</v>
+      </c>
+      <c r="C17" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D17" s="75">
+        <v>136083127</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450203548</v>
+      </c>
+      <c r="F17" s="71" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="44">
+        <v>46024</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="44"/>
+      <c r="B18" s="7">
+        <v>46024</v>
+      </c>
+      <c r="C18" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D18" s="75">
+        <v>136085372</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450203889</v>
+      </c>
+      <c r="F18" s="71" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="44">
+        <v>46024</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="44"/>
+      <c r="B19" s="7">
+        <v>46031</v>
+      </c>
+      <c r="C19" s="54">
+        <v>46035</v>
+      </c>
+      <c r="D19" s="75">
+        <v>136188472</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450213415</v>
+      </c>
+      <c r="F19" s="71" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="44">
+        <v>46031</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="31"/>
       <c r="G20" s="42"/>
       <c r="H20" s="12"/>
       <c r="I20" s="44"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="55"/>
+      <c r="C21" s="54"/>
       <c r="D21" s="22"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
@@ -1798,11 +2157,9 @@
       <c r="I21" s="44"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="55"/>
+      <c r="C22" s="54"/>
       <c r="D22" s="22"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
@@ -1811,11 +2168,9 @@
       <c r="I22" s="44"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="55"/>
+      <c r="C23" s="54"/>
       <c r="D23" s="22"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11"/>
@@ -1824,11 +2179,9 @@
       <c r="I23" s="44"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="55"/>
+      <c r="C24" s="54"/>
       <c r="D24" s="22"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
@@ -1837,11 +2190,9 @@
       <c r="I24" s="44"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="55"/>
+      <c r="C25" s="54"/>
       <c r="D25" s="22"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
@@ -1850,11 +2201,9 @@
       <c r="I25" s="44"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="55"/>
+      <c r="C26" s="54"/>
       <c r="D26" s="22"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
@@ -1863,11 +2212,9 @@
       <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="55"/>
+      <c r="C27" s="54"/>
       <c r="D27" s="22"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
@@ -1875,96 +2222,17 @@
       <c r="H27" s="12"/>
       <c r="I27" s="44"/>
     </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="44"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="44"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="44"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="44"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="44"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="24"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:F32">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A32" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A27" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G27" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2020,20 +2288,20 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="60"/>
+      <c r="B2" s="58"/>
       <c r="C2" s="25"/>
       <c r="D2" s="26"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
       <c r="G2" s="19"/>
-      <c r="H2" s="61"/>
+      <c r="H2" s="59"/>
       <c r="I2" s="44"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="60"/>
+      <c r="B3" s="58"/>
       <c r="C3" s="25"/>
       <c r="D3" s="26"/>
       <c r="E3" s="17"/>
@@ -2061,18 +2329,18 @@
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="25"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="67"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="65"/>
       <c r="I5" s="48"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="60"/>
+      <c r="B6" s="58"/>
       <c r="C6" s="25"/>
       <c r="D6" s="22"/>
       <c r="E6" s="17"/>
@@ -2085,7 +2353,7 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="60"/>
+      <c r="B7" s="58"/>
       <c r="C7" s="25"/>
       <c r="D7" s="22"/>
       <c r="E7" s="17"/>
@@ -2098,7 +2366,7 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="60"/>
+      <c r="B8" s="58"/>
       <c r="C8" s="25"/>
       <c r="D8" s="22"/>
       <c r="E8" s="17"/>
@@ -2111,7 +2379,7 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="60"/>
+      <c r="B9" s="58"/>
       <c r="C9" s="25"/>
       <c r="D9" s="22"/>
       <c r="E9" s="17"/>
@@ -2124,12 +2392,12 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="60"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="25"/>
       <c r="D10" s="22"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="62"/>
+      <c r="G10" s="60"/>
       <c r="H10" s="12"/>
       <c r="I10" s="44"/>
     </row>
@@ -2137,7 +2405,7 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="60"/>
+      <c r="B11" s="58"/>
       <c r="C11" s="25"/>
       <c r="D11" s="22"/>
       <c r="E11" s="17"/>
@@ -2150,12 +2418,12 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="60"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="25"/>
       <c r="D12" s="22"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="62"/>
+      <c r="G12" s="60"/>
       <c r="H12" s="12"/>
       <c r="I12" s="44"/>
     </row>
@@ -2163,7 +2431,7 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="60"/>
+      <c r="B13" s="58"/>
       <c r="C13" s="25"/>
       <c r="D13" s="22"/>
       <c r="E13" s="17"/>
@@ -2176,7 +2444,7 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="60"/>
+      <c r="B14" s="58"/>
       <c r="C14" s="25"/>
       <c r="D14" s="22"/>
       <c r="E14" s="17"/>
@@ -2189,12 +2457,12 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="60"/>
+      <c r="B15" s="58"/>
       <c r="C15" s="25"/>
       <c r="D15" s="22"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="62"/>
+      <c r="G15" s="60"/>
       <c r="H15" s="12"/>
       <c r="I15" s="44"/>
     </row>
@@ -2202,7 +2470,7 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="60"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="25"/>
       <c r="D16" s="22"/>
       <c r="E16" s="17"/>
@@ -2215,7 +2483,7 @@
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="60"/>
+      <c r="B17" s="58"/>
       <c r="C17" s="25"/>
       <c r="D17" s="22"/>
       <c r="E17" s="17"/>
@@ -2272,7 +2540,7 @@
       <c r="D21" s="22"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="62"/>
+      <c r="G21" s="60"/>
       <c r="H21" s="12"/>
       <c r="I21" s="44"/>
     </row>
@@ -2293,10 +2561,10 @@
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="25"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="56"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="55"/>
       <c r="F23" s="31"/>
-      <c r="G23" s="69"/>
+      <c r="G23" s="67"/>
       <c r="H23" s="14"/>
     </row>
     <row r="24" spans="1:9">
@@ -4999,57 +5267,55 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540081</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-540081</Url>
-      <Description>QAFFA7D2F2TC-2102087286-540081</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14537913923f18b595a8efb93d476f56">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c805678a1a23774ee476d175eb06e332" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5427,68 +5693,70 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540081</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-540081</Url>
+      <Description>QAFFA7D2F2TC-2102087286-540081</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3044653F-FFF3-4CD8-AD32-945189407B2B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3044653F-FFF3-4CD8-AD32-945189407B2B}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 12.01.2026 a 18.01.2026.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 12.01.2026 a 18.01.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{362DBC96-E4D9-4616-BF30-1479A34B965E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A421CB4A-280A-4B07-993E-005DE541414E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="12.01" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="116">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -222,6 +222,186 @@
   </si>
   <si>
     <t xml:space="preserve">THIAGO SILVA QUEIROZ SANTANA                 </t>
+  </si>
+  <si>
+    <t>14/01/2026</t>
+  </si>
+  <si>
+    <t>ANDRE EDUARDO YOSHIDA CPF 20601354869</t>
+  </si>
+  <si>
+    <t>Veículo em duplicidade com outra  proposta</t>
+  </si>
+  <si>
+    <t>SIM</t>
+  </si>
+  <si>
+    <t>M G COMERCIO DE TECIDOS E AVIAMENTOS EM GERAL</t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Traseira e lateral do motorista, Painel com carro ligado, Chassi Justificativa de Dados Divergentes: Fotos que tiveram repique: Traseira e lateral do motorista, Painel com carro ligado, Chassi</t>
+  </si>
+  <si>
+    <t>PAO DE ACUCAR ALIMENTOS ATACADO VAREJO LTDA M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGINALDO PIZANE DE AZEVEDO                  </t>
+  </si>
+  <si>
+    <t>RECUSA: *PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Documento do veículo, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGRID SCHNABEL                              </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: CHASSI (LOCAL INCORRETO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAYCON MAURICIO GARCIA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUADALAJARA DE FATIMA MONTANHERI ARAUJO      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARMEN LUCIA CAVATAO DE SOUZA                </t>
+  </si>
+  <si>
+    <t>RECUSA: SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO EXPIRADO Fotos: Frente e lateral do passageiro, Porta malas aberto, Frente e lateral do motorista.</t>
+  </si>
+  <si>
+    <t>ARIANO GERMANO PECAS E SERVICOS AUTOMOVEIS LT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONICA SOARES DE ASSIS                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE HELIO RIGONATO DE ANDRADE               </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro, Frente e lateral do motorista (Não enquadrada), Porta malas aberto (Com objetos dentro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMANUELLA CERVEIRA DE ANDRADE CUNHA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GELOUCOS COMERCIO DE GELOS LTDA ME           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITOR MORAES SANTOS                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIA BATISTA DO NASCIMENTO ME               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIANA SILVA DE MELO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAIQUE AUGUSTO DE LIMA                       </t>
+  </si>
+  <si>
+    <t>Bônus;</t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não h
+á possibilidade efetuar a transferência de bônus para o(a) senhor(
+a) KAIQUE AUGUSTO DE LIMA, pois este não consta como condutor na a
+pólice anterior. &lt;br&gt;Neste caso, iremos realizar a recusa desta p
+roposta, para conclusão do processo é necessário informar o e-mail
+do segurado anterior ADEMIR GOMES DE LIMA, para que o mesmo també
+m fique ciente da recusa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO MARCELO NARCHIN                         </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: CHASSI. KM TOTAL INDISP. ESCAPAMENTO ALTERADO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA REGIANE SOARES SILVA                   </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro e do motorista, Traseira e lateral do motorista e do passageiro, Motor (Nao enquadrada corretamente) Painel com carro ligado, (Veiculo desligado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSILDA FELIPE DOS SANTOS                    </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Chassi (Local incorreto) Justificativa de Dados Divergentes: CRLV em nome de terceiros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDER DE SOUZA                              </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Painel com a motocicleta ligada, Lateral esquerda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARMANDO GALLI NETO                           </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Painel com a motocicleta ligada, Traseira ESCAPAMENTO ARRAN :1 PT TANQUE AMASSA: 1PT LATERAL ESQ ARRAN :1 PT PARA LAMA TRAS ARRAN : 1PT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APARECIDA DE LOURDES LOPES                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Chassi. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE AUDI OLIVEIRA DA SILVA                  </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE N CORRIGIU AS FOTOS INCORRETAS - PRAZO EXP FOTOS INCORRETAS: Frente e lateral do passageiro e motorista, Traseira e lateral do motorista e do passageiro, Painel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELMA DE OLIVEIRA DO NASCIMENTO              </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO** PRAZO EXPIRADO: cliente enviou as fotos no prazo final não dando tempo de correção - chassi local errado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA PAULA SANTOS DA SILVA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO/ PRAZO EXPIRADO/ FOTOS NAO CORRIGIDAS: CHASSI/ LATERAL ESQ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERCIO MAGNER DE OLIVEIRA                     </t>
+  </si>
+  <si>
+    <t>SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO EXPIRADO FOTOS: Frente e lateral do passageiro, Traseira e lateral do motorista, Frente e lateral do motorista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA MAYARA PEREIRA DA SILVA DIAS           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JESSICA DOS SANTOS SOUZA                     </t>
+  </si>
+  <si>
+    <t>*PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Documento do veículo, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THATY LUZ DE MEDEIROS                        </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade efetuar a transferência de bônus para o(a) senhor(a) T
+HATYLUZ DE MEDEIROS, pois este não consta como condutor na apólice
+anterior. &lt;br&gt;&lt;br&gt;Neste caso, iremos realizar a recusa desta pro
+posta, para conclusão do processo é necessário informar o email do
+seguradoanterior (ROBSON DA SILVA CARDOSO), para que o mesmo tamb
+ém fique ciente da recusa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADINAEL LOPES PAMPONET                       </t>
+  </si>
+  <si>
+    <t>PRAZO EXPIRADO * repique: Frente e lateral do passageiro, Traseira e lateral do motorista, Painel com carro ligado, Documento do veículo, Frente e lateral do motorista, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KEROLAINE SANTOS PINHEIRO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedido do segurado </t>
   </si>
 </sst>
 </file>
@@ -280,7 +460,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -523,12 +703,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -681,23 +899,14 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -710,7 +919,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -720,10 +928,27 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1111,19 +1336,19 @@
       <c r="C2" s="25">
         <v>46034</v>
       </c>
-      <c r="D2" s="69" t="s">
+      <c r="D2" s="66" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="22">
         <v>3450211677</v>
       </c>
-      <c r="F2" s="63" t="s">
+      <c r="F2" s="61" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="61" t="s">
         <v>13</v>
       </c>
       <c r="I2" s="44"/>
@@ -1147,7 +1372,7 @@
       <c r="F3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="65" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="45" t="s">
@@ -1176,7 +1401,7 @@
       <c r="F4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="65" t="s">
         <v>18</v>
       </c>
       <c r="H4" s="45" t="s">
@@ -1205,7 +1430,7 @@
       <c r="F5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="65" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="45" t="s">
@@ -1234,7 +1459,7 @@
       <c r="F6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="68" t="s">
+      <c r="G6" s="65" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="45" t="s">
@@ -1263,7 +1488,7 @@
       <c r="F7" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="68" t="s">
+      <c r="G7" s="65" t="s">
         <v>25</v>
       </c>
       <c r="H7" s="46" t="s">
@@ -1292,7 +1517,7 @@
       <c r="F8" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="68" t="s">
+      <c r="G8" s="65" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="46" t="s">
@@ -1321,7 +1546,7 @@
       <c r="F9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="65" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="45" t="s">
@@ -1350,7 +1575,7 @@
       <c r="F10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="68" t="s">
+      <c r="G10" s="65" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="45" t="s">
@@ -1379,7 +1604,7 @@
       <c r="F11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="68" t="s">
+      <c r="G11" s="65" t="s">
         <v>18</v>
       </c>
       <c r="H11" s="45" t="s">
@@ -1408,7 +1633,7 @@
       <c r="F12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="65" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="45" t="s">
@@ -1422,7 +1647,7 @@
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="25"/>
-      <c r="D13" s="70"/>
+      <c r="D13" s="67"/>
       <c r="E13" s="55"/>
       <c r="F13" s="31"/>
       <c r="G13" s="42"/>
@@ -1593,13 +1818,13 @@
       <c r="C1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="73" t="s">
+      <c r="D1" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="73" t="s">
+      <c r="E1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="74" t="s">
+      <c r="F1" s="70" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="50" t="s">
@@ -1622,16 +1847,16 @@
       <c r="C2" s="54">
         <v>46035</v>
       </c>
-      <c r="D2" s="75">
+      <c r="D2" s="22">
         <v>136076382</v>
       </c>
       <c r="E2" s="17">
         <v>3450202877</v>
       </c>
-      <c r="F2" s="71" t="s">
+      <c r="F2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="72" t="s">
+      <c r="G2" s="68" t="s">
         <v>25</v>
       </c>
       <c r="H2" s="31" t="s">
@@ -1651,19 +1876,19 @@
       <c r="C3" s="54">
         <v>46035</v>
       </c>
-      <c r="D3" s="75">
+      <c r="D3" s="22">
         <v>136088990</v>
       </c>
       <c r="E3" s="17">
         <v>3450204439</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="76" t="s">
+      <c r="H3" s="12" t="s">
         <v>39</v>
       </c>
       <c r="I3" s="44">
@@ -1680,16 +1905,16 @@
       <c r="C4" s="54">
         <v>46035</v>
       </c>
-      <c r="D4" s="75">
+      <c r="D4" s="22">
         <v>136078456</v>
       </c>
       <c r="E4" s="17">
         <v>3450189061</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="65" t="s">
         <v>25</v>
       </c>
       <c r="H4" s="12" t="s">
@@ -1709,16 +1934,16 @@
       <c r="C5" s="54">
         <v>46035</v>
       </c>
-      <c r="D5" s="75">
+      <c r="D5" s="22">
         <v>136098801</v>
       </c>
       <c r="E5" s="17">
         <v>3450205352</v>
       </c>
-      <c r="F5" s="71" t="s">
+      <c r="F5" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="65" t="s">
         <v>25</v>
       </c>
       <c r="H5" s="12" t="s">
@@ -1738,16 +1963,16 @@
       <c r="C6" s="54">
         <v>46035</v>
       </c>
-      <c r="D6" s="75">
+      <c r="D6" s="22">
         <v>136104011</v>
       </c>
       <c r="E6" s="17">
         <v>3450205803</v>
       </c>
-      <c r="F6" s="71" t="s">
+      <c r="F6" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="68" t="s">
+      <c r="G6" s="65" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="12" t="s">
@@ -1767,16 +1992,16 @@
       <c r="C7" s="54">
         <v>46035</v>
       </c>
-      <c r="D7" s="75">
+      <c r="D7" s="22">
         <v>136110987</v>
       </c>
       <c r="E7" s="17">
         <v>3450195947</v>
       </c>
-      <c r="F7" s="71" t="s">
+      <c r="F7" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="68" t="s">
+      <c r="G7" s="65" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="11" t="s">
@@ -1796,16 +2021,16 @@
       <c r="C8" s="54">
         <v>46035</v>
       </c>
-      <c r="D8" s="75">
+      <c r="D8" s="22">
         <v>136170856</v>
       </c>
       <c r="E8" s="17">
         <v>3450211226</v>
       </c>
-      <c r="F8" s="71" t="s">
+      <c r="F8" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="68" t="s">
+      <c r="G8" s="65" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="11" t="s">
@@ -1825,16 +2050,16 @@
       <c r="C9" s="54">
         <v>46035</v>
       </c>
-      <c r="D9" s="75">
+      <c r="D9" s="22">
         <v>136140036</v>
       </c>
       <c r="E9" s="17">
         <v>3450209246</v>
       </c>
-      <c r="F9" s="71" t="s">
+      <c r="F9" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="65" t="s">
         <v>48</v>
       </c>
       <c r="H9" s="12" t="s">
@@ -1854,16 +2079,16 @@
       <c r="C10" s="54">
         <v>46035</v>
       </c>
-      <c r="D10" s="75">
+      <c r="D10" s="22">
         <v>136184781</v>
       </c>
       <c r="E10" s="17">
         <v>3450212975</v>
       </c>
-      <c r="F10" s="71" t="s">
+      <c r="F10" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="68" t="s">
+      <c r="G10" s="65" t="s">
         <v>18</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -1883,16 +2108,16 @@
       <c r="C11" s="54">
         <v>46035</v>
       </c>
-      <c r="D11" s="75">
+      <c r="D11" s="22">
         <v>136170601</v>
       </c>
       <c r="E11" s="17">
         <v>3450211523</v>
       </c>
-      <c r="F11" s="71" t="s">
+      <c r="F11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="68" t="s">
+      <c r="G11" s="65" t="s">
         <v>18</v>
       </c>
       <c r="H11" s="12" t="s">
@@ -1912,16 +2137,16 @@
       <c r="C12" s="54">
         <v>46035</v>
       </c>
-      <c r="D12" s="75">
+      <c r="D12" s="22">
         <v>136074390</v>
       </c>
       <c r="E12" s="17">
         <v>3450202712</v>
       </c>
-      <c r="F12" s="71" t="s">
+      <c r="F12" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="65" t="s">
         <v>25</v>
       </c>
       <c r="H12" s="12" t="s">
@@ -1941,16 +2166,16 @@
       <c r="C13" s="54">
         <v>46035</v>
       </c>
-      <c r="D13" s="75">
+      <c r="D13" s="22">
         <v>136075052</v>
       </c>
       <c r="E13" s="17">
         <v>3450202756</v>
       </c>
-      <c r="F13" s="71" t="s">
+      <c r="F13" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="68" t="s">
+      <c r="G13" s="65" t="s">
         <v>25</v>
       </c>
       <c r="H13" s="12" t="s">
@@ -1970,16 +2195,16 @@
       <c r="C14" s="54">
         <v>46035</v>
       </c>
-      <c r="D14" s="75">
+      <c r="D14" s="22">
         <v>136075688</v>
       </c>
       <c r="E14" s="17">
         <v>3450202811</v>
       </c>
-      <c r="F14" s="71" t="s">
+      <c r="F14" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G14" s="68" t="s">
+      <c r="G14" s="65" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="12" t="s">
@@ -1999,16 +2224,16 @@
       <c r="C15" s="54">
         <v>46035</v>
       </c>
-      <c r="D15" s="75">
+      <c r="D15" s="22">
         <v>136078295</v>
       </c>
       <c r="E15" s="17">
         <v>3450202657</v>
       </c>
-      <c r="F15" s="71" t="s">
+      <c r="F15" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="68" t="s">
+      <c r="G15" s="65" t="s">
         <v>25</v>
       </c>
       <c r="H15" s="12" t="s">
@@ -2028,16 +2253,16 @@
       <c r="C16" s="54">
         <v>46035</v>
       </c>
-      <c r="D16" s="75">
+      <c r="D16" s="22">
         <v>136081242</v>
       </c>
       <c r="E16" s="17">
         <v>3450203251</v>
       </c>
-      <c r="F16" s="71" t="s">
+      <c r="F16" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="68" t="s">
+      <c r="G16" s="65" t="s">
         <v>25</v>
       </c>
       <c r="H16" s="12" t="s">
@@ -2057,16 +2282,16 @@
       <c r="C17" s="54">
         <v>46035</v>
       </c>
-      <c r="D17" s="75">
+      <c r="D17" s="22">
         <v>136083127</v>
       </c>
       <c r="E17" s="17">
         <v>3450203548</v>
       </c>
-      <c r="F17" s="71" t="s">
+      <c r="F17" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="68" t="s">
+      <c r="G17" s="65" t="s">
         <v>25</v>
       </c>
       <c r="H17" s="12" t="s">
@@ -2086,16 +2311,16 @@
       <c r="C18" s="54">
         <v>46035</v>
       </c>
-      <c r="D18" s="75">
+      <c r="D18" s="22">
         <v>136085372</v>
       </c>
       <c r="E18" s="17">
         <v>3450203889</v>
       </c>
-      <c r="F18" s="71" t="s">
+      <c r="F18" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="68" t="s">
+      <c r="G18" s="65" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="12" t="s">
@@ -2115,16 +2340,16 @@
       <c r="C19" s="54">
         <v>46035</v>
       </c>
-      <c r="D19" s="75">
+      <c r="D19" s="22">
         <v>136188472</v>
       </c>
       <c r="E19" s="17">
         <v>3450213415</v>
       </c>
-      <c r="F19" s="71" t="s">
+      <c r="F19" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="68" t="s">
+      <c r="G19" s="65" t="s">
         <v>18</v>
       </c>
       <c r="H19" s="12" t="s">
@@ -2242,16 +2467,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.85546875" style="16" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" style="16" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="16" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" style="16" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" style="16" customWidth="1"/>
     <col min="6" max="6" width="30.140625" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.5703125" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" customWidth="1"/>
+    <col min="8" max="8" width="37.7109375" customWidth="1"/>
     <col min="9" max="9" width="21" style="24" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2288,472 +2514,1006 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="44"/>
+      <c r="B2" s="58">
+        <v>46054</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="60" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450203493</v>
+      </c>
+      <c r="F2" s="61" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="59" t="s">
+        <v>62</v>
+      </c>
+      <c r="I2" s="44" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="44"/>
+      <c r="B3" s="58">
+        <v>46028</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="22">
+        <v>136120926</v>
+      </c>
+      <c r="E3" s="72">
+        <v>3450207079</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="44">
+        <v>46028</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="44"/>
+      <c r="B4" s="58">
+        <v>46029</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="22">
+        <v>136140208</v>
+      </c>
+      <c r="E4" s="72">
+        <v>3450209279</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="44">
+        <v>46029</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="48"/>
+      <c r="B5" s="58">
+        <v>46029</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="22">
+        <v>136136791</v>
+      </c>
+      <c r="E5" s="73">
+        <v>3450208740</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="48">
+        <v>46029</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="44"/>
+      <c r="B6" s="58">
+        <v>46029</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="22">
+        <v>136139896</v>
+      </c>
+      <c r="E6" s="72">
+        <v>3450209213</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" s="44">
+        <v>46029</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="44"/>
+      <c r="B7" s="58">
+        <v>46030</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="22">
+        <v>136167514</v>
+      </c>
+      <c r="E7" s="72">
+        <v>3450211358</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="44">
+        <v>46030</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="44"/>
+      <c r="B8" s="58">
+        <v>46030</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="22">
+        <v>136165719</v>
+      </c>
+      <c r="E8" s="72">
+        <v>3450211215</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="44">
+        <v>46030</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="44"/>
+      <c r="B9" s="58">
+        <v>46030</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="22">
+        <v>136168912</v>
+      </c>
+      <c r="E9" s="72">
+        <v>3450211479</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" s="44">
+        <v>46030</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="44"/>
+      <c r="B10" s="58">
+        <v>46031</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="22">
+        <v>136190707</v>
+      </c>
+      <c r="E10" s="72">
+        <v>3450213547</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="44">
+        <v>46031</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="44"/>
+      <c r="B11" s="58">
+        <v>46031</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="22">
+        <v>136183161</v>
+      </c>
+      <c r="E11" s="72">
+        <v>3450212843</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" s="44">
+        <v>46031</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="44"/>
+      <c r="B12" s="58">
+        <v>46029</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="22">
+        <v>136154789</v>
+      </c>
+      <c r="E12" s="72">
+        <v>3450209170</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="71" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="44">
+        <v>46029</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="44"/>
+      <c r="B13" s="58">
+        <v>46031</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="22">
+        <v>136195999</v>
+      </c>
+      <c r="E13" s="72">
+        <v>3450213195</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="44">
+        <v>46031</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="44"/>
+      <c r="B14" s="58">
+        <v>46034</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="22">
+        <v>136200707</v>
+      </c>
+      <c r="E14" s="72">
+        <v>3450214108</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="44">
+        <v>46034</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="44"/>
+      <c r="B15" s="58">
+        <v>46034</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="22">
+        <v>136201925</v>
+      </c>
+      <c r="E15" s="72">
+        <v>3450214284</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="44">
+        <v>46034</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="58"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="44"/>
+      <c r="B16" s="58">
+        <v>46034</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="22">
+        <v>136208398</v>
+      </c>
+      <c r="E16" s="72">
+        <v>3450214801</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="44">
+        <v>46034</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="44"/>
+      <c r="B17" s="58">
+        <v>46034</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="22">
+        <v>136195940</v>
+      </c>
+      <c r="E17" s="72">
+        <v>3450213745</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="44">
+        <v>46034</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="44"/>
+      <c r="B18" s="7">
+        <v>46035</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="22">
+        <v>136222069</v>
+      </c>
+      <c r="E18" s="72">
+        <v>3450215901</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="44">
+        <v>46035</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="44"/>
+      <c r="B19" s="7">
+        <v>46021</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="22">
+        <v>136056633</v>
+      </c>
+      <c r="E19" s="72">
+        <v>3450201030</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="65" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="78" t="s">
+        <v>86</v>
+      </c>
+      <c r="I19" s="44">
+        <v>46031</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="44"/>
+      <c r="B20" s="7">
+        <v>46029</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="22">
+        <v>136141351</v>
+      </c>
+      <c r="E20" s="72">
+        <v>3450209334</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="71" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" s="44">
+        <v>46029</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="44"/>
+      <c r="B21" s="7">
+        <v>46029</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="22">
+        <v>136134337</v>
+      </c>
+      <c r="E21" s="72">
+        <v>3450208454</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I21" s="48">
+        <v>46029</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="44"/>
+      <c r="B22" s="7">
+        <v>46028</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="22">
+        <v>136130857</v>
+      </c>
+      <c r="E22" s="74">
+        <v>3450206848</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="59" t="s">
+        <v>92</v>
+      </c>
+      <c r="I22" s="44">
+        <v>46028</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="14"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46028</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="22">
+        <v>136118482</v>
+      </c>
+      <c r="E23" s="72">
+        <v>3450206815</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23" s="44">
+        <v>46028</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>46029</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="22">
+        <v>136138272</v>
+      </c>
+      <c r="E24" s="72">
+        <v>3450209114</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="I24" s="44">
+        <v>46029</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>46030</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="22">
+        <v>136155426</v>
+      </c>
+      <c r="E25" s="72">
+        <v>3450210071</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="I25" s="44">
+        <v>46030</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46030</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="22">
+        <v>136162298</v>
+      </c>
+      <c r="E26" s="72">
+        <v>3450210885</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="77" t="s">
+        <v>100</v>
+      </c>
+      <c r="I26" s="44">
+        <v>46030</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46030</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="22">
+        <v>136161496</v>
+      </c>
+      <c r="E27" s="72">
+        <v>3450210709</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="77" t="s">
+        <v>102</v>
+      </c>
+      <c r="I27" s="44">
+        <v>46030</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46030</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="22">
+        <v>136155957</v>
+      </c>
+      <c r="E28" s="72">
+        <v>3450210160</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="77" t="s">
+        <v>104</v>
+      </c>
+      <c r="I28" s="44">
+        <v>46030</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46030</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="22">
+        <v>136160145</v>
+      </c>
+      <c r="E29" s="72">
+        <v>3450210588</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="I29" s="44">
+        <v>46030</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="9"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46028</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="22">
+        <v>136123401</v>
+      </c>
+      <c r="E30" s="72">
+        <v>3450207321</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="77" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="44">
+        <v>46028</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="9"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46030</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="22">
+        <v>136166789</v>
+      </c>
+      <c r="E31" s="75">
+        <v>3450211303</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="77" t="s">
+        <v>109</v>
+      </c>
+      <c r="I31" s="44">
+        <v>46030</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46028</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" s="22">
+        <v>136115013</v>
+      </c>
+      <c r="E32" s="76">
+        <v>3450206397</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="H32" s="79" t="s">
+        <v>111</v>
+      </c>
+      <c r="I32" s="44">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46030</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" s="22">
+        <v>136163758</v>
+      </c>
+      <c r="E33" s="76">
+        <v>3450211040</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="77" t="s">
+        <v>113</v>
+      </c>
+      <c r="I33" s="44">
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46058</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D34" s="22">
+        <v>136120283</v>
+      </c>
+      <c r="E34" s="76">
+        <v>3450206991</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="H34" s="77" t="s">
+        <v>115</v>
+      </c>
+      <c r="I34" s="44">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="8"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="D35" s="20"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="77"/>
+      <c r="I35" s="44"/>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="8"/>
       <c r="C36" s="7"/>
       <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="E36" s="13"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="44"/>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="8"/>
       <c r="C37" s="7"/>
       <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="44"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A23:A33" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+  <dataValidations count="3">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B17" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G30" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A34" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B17" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5266,56 +6026,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14537913923f18b595a8efb93d476f56">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c805678a1a23774ee476d175eb06e332" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5693,7 +6403,66 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540081</_dlc_DocId>
@@ -5736,27 +6505,18 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3044653F-FFF3-4CD8-AD32-945189407B2B}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3044653F-FFF3-4CD8-AD32-945189407B2B}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>